--- a/Experiment/finance/salary.xlsx
+++ b/Experiment/finance/salary.xlsx
@@ -468,10 +468,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>65000</v>
+        <v>85000</v>
       </c>
       <c r="E2" t="n">
-        <v>6500</v>
+        <v>8500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>160000</v>
+        <v>135000</v>
       </c>
       <c r="E3" t="n">
-        <v>16000</v>
+        <v>13500</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>160000</v>
+        <v>65000</v>
       </c>
       <c r="E4" t="n">
-        <v>16000</v>
+        <v>6500</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>85000</v>
+        <v>135000</v>
       </c>
       <c r="E5" t="n">
-        <v>8500</v>
+        <v>13500</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>160000</v>
+        <v>65000</v>
       </c>
       <c r="E6" t="n">
-        <v>16000</v>
+        <v>6500</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,10 +623,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>160000</v>
+        <v>85000</v>
       </c>
       <c r="E7" t="n">
-        <v>16000</v>
+        <v>8500</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>110000</v>
+        <v>135000</v>
       </c>
       <c r="E8" t="n">
-        <v>11000</v>
+        <v>13500</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>85000</v>
+        <v>135000</v>
       </c>
       <c r="E10" t="n">
-        <v>8500</v>
+        <v>13500</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>110000</v>
+        <v>65000</v>
       </c>
       <c r="E11" t="n">
-        <v>11000</v>
+        <v>6500</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>185000</v>
+        <v>110000</v>
       </c>
       <c r="E12" t="n">
-        <v>18500</v>
+        <v>11000</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>135000</v>
+        <v>65000</v>
       </c>
       <c r="E13" t="n">
-        <v>13500</v>
+        <v>6500</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>110000</v>
+        <v>135000</v>
       </c>
       <c r="E14" t="n">
-        <v>11000</v>
+        <v>13500</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>185000</v>
+        <v>65000</v>
       </c>
       <c r="E16" t="n">
-        <v>18500</v>
+        <v>6500</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>

--- a/Experiment/finance/salary.xlsx
+++ b/Experiment/finance/salary.xlsx
@@ -468,10 +468,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>85000</v>
+        <v>185000</v>
       </c>
       <c r="E2" t="n">
-        <v>8500</v>
+        <v>18500</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>135000</v>
+        <v>110000</v>
       </c>
       <c r="E3" t="n">
-        <v>13500</v>
+        <v>11000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>65000</v>
+        <v>160000</v>
       </c>
       <c r="E4" t="n">
-        <v>6500</v>
+        <v>16000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>135000</v>
+        <v>110000</v>
       </c>
       <c r="E5" t="n">
-        <v>13500</v>
+        <v>11000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>65000</v>
+        <v>160000</v>
       </c>
       <c r="E6" t="n">
-        <v>6500</v>
+        <v>16000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>110000</v>
+        <v>135000</v>
       </c>
       <c r="E9" t="n">
-        <v>11000</v>
+        <v>13500</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>65000</v>
+        <v>110000</v>
       </c>
       <c r="E11" t="n">
-        <v>6500</v>
+        <v>11000</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>65000</v>
+        <v>85000</v>
       </c>
       <c r="E13" t="n">
-        <v>6500</v>
+        <v>8500</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>135000</v>
+        <v>85000</v>
       </c>
       <c r="E14" t="n">
-        <v>13500</v>
+        <v>8500</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
